--- a/Team-Data/2012-13/3-27-2012-13.xlsx
+++ b/Team-Data/2012-13/3-27-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F2" t="n">
         <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>0.556</v>
+        <v>0.549</v>
       </c>
       <c r="H2" t="n">
         <v>48.5</v>
@@ -691,7 +758,7 @@
         <v>23.4</v>
       </c>
       <c r="N2" t="n">
-        <v>0.379</v>
+        <v>0.378</v>
       </c>
       <c r="O2" t="n">
         <v>13.6</v>
@@ -700,7 +767,7 @@
         <v>19.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.709</v>
+        <v>0.707</v>
       </c>
       <c r="R2" t="n">
         <v>9.199999999999999</v>
@@ -715,40 +782,40 @@
         <v>24.6</v>
       </c>
       <c r="V2" t="n">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="W2" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA2" t="n">
         <v>18.6</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.7</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE2" t="n">
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AG2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AH2" t="n">
         <v>11</v>
@@ -775,7 +842,7 @@
         <v>28</v>
       </c>
       <c r="AP2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ2" t="n">
         <v>26</v>
@@ -793,7 +860,7 @@
         <v>2</v>
       </c>
       <c r="AV2" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AW2" t="n">
         <v>15</v>
@@ -805,7 +872,7 @@
         <v>7</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
         <v>26</v>
@@ -814,7 +881,7 @@
         <v>15</v>
       </c>
       <c r="BC2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -843,16 +910,16 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
         <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>0.521</v>
+        <v>0.514</v>
       </c>
       <c r="H3" t="n">
         <v>49.1</v>
@@ -861,7 +928,7 @@
         <v>36.7</v>
       </c>
       <c r="J3" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K3" t="n">
         <v>0.461</v>
@@ -870,31 +937,31 @@
         <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.9</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
         <v>0.356</v>
       </c>
       <c r="O3" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="P3" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.777</v>
+        <v>0.778</v>
       </c>
       <c r="R3" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="T3" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="U3" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V3" t="n">
         <v>14.7</v>
@@ -903,7 +970,7 @@
         <v>8.4</v>
       </c>
       <c r="X3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y3" t="n">
         <v>4.8</v>
@@ -912,16 +979,16 @@
         <v>21.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB3" t="n">
-        <v>95.90000000000001</v>
+        <v>96</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>14</v>
@@ -951,13 +1018,13 @@
         <v>27</v>
       </c>
       <c r="AN3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO3" t="n">
         <v>18</v>
       </c>
       <c r="AP3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
         <v>8</v>
@@ -966,16 +1033,16 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AT3" t="n">
         <v>29</v>
       </c>
       <c r="AU3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV3" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW3" t="n">
         <v>7</v>
@@ -984,16 +1051,16 @@
         <v>24</v>
       </c>
       <c r="AY3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F4" t="n">
         <v>29</v>
       </c>
       <c r="G4" t="n">
-        <v>0.592</v>
+        <v>0.586</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J4" t="n">
-        <v>79.59999999999999</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L4" t="n">
         <v>7.7</v>
       </c>
       <c r="M4" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.358</v>
+        <v>0.359</v>
       </c>
       <c r="O4" t="n">
         <v>17.4</v>
@@ -1064,28 +1131,28 @@
         <v>23.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.737</v>
+        <v>0.74</v>
       </c>
       <c r="R4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="S4" t="n">
         <v>30.1</v>
       </c>
       <c r="T4" t="n">
-        <v>42.7</v>
+        <v>42.6</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
         <v>14.7</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y4" t="n">
         <v>4.8</v>
@@ -1097,13 +1164,13 @@
         <v>21.2</v>
       </c>
       <c r="AB4" t="n">
-        <v>96.09999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>9</v>
@@ -1118,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="AI4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ4" t="n">
         <v>28</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO4" t="n">
         <v>11</v>
@@ -1142,22 +1209,22 @@
         <v>8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AR4" t="n">
         <v>6</v>
       </c>
       <c r="AS4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU4" t="n">
         <v>28</v>
       </c>
       <c r="AV4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AW4" t="n">
         <v>23</v>
@@ -1175,7 +1242,7 @@
         <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1207,28 +1274,28 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" t="n">
         <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>0.239</v>
+        <v>0.229</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>34.3</v>
+        <v>34.1</v>
       </c>
       <c r="J5" t="n">
-        <v>81.59999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.42</v>
+        <v>0.419</v>
       </c>
       <c r="L5" t="n">
         <v>5.7</v>
@@ -1237,7 +1304,7 @@
         <v>17</v>
       </c>
       <c r="N5" t="n">
-        <v>0.336</v>
+        <v>0.337</v>
       </c>
       <c r="O5" t="n">
         <v>19.1</v>
@@ -1252,13 +1319,13 @@
         <v>11.3</v>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T5" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U5" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V5" t="n">
         <v>13.8</v>
@@ -1273,25 +1340,25 @@
         <v>7.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="AA5" t="n">
         <v>21.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>93.40000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-9.699999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>30</v>
       </c>
       <c r="AF5" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG5" t="n">
         <v>30</v>
@@ -1342,7 +1409,7 @@
         <v>5</v>
       </c>
       <c r="AW5" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AX5" t="n">
         <v>6</v>
@@ -1357,7 +1424,7 @@
         <v>5</v>
       </c>
       <c r="BB5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC5" t="n">
         <v>30</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1389,16 +1456,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E6" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F6" t="n">
         <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.551</v>
       </c>
       <c r="H6" t="n">
         <v>48.4</v>
@@ -1407,7 +1474,7 @@
         <v>35.7</v>
       </c>
       <c r="J6" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K6" t="n">
         <v>0.436</v>
@@ -1416,7 +1483,7 @@
         <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="N6" t="n">
         <v>0.34</v>
@@ -1425,13 +1492,13 @@
         <v>16.5</v>
       </c>
       <c r="P6" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0.783</v>
       </c>
       <c r="R6" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S6" t="n">
         <v>30.7</v>
@@ -1449,10 +1516,10 @@
         <v>7.3</v>
       </c>
       <c r="X6" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="Y6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z6" t="n">
         <v>19.5</v>
@@ -1461,7 +1528,7 @@
         <v>19.7</v>
       </c>
       <c r="AB6" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0.5</v>
@@ -1470,13 +1537,13 @@
         <v>26</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF6" t="n">
         <v>10</v>
       </c>
       <c r="AG6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
@@ -1485,10 +1552,10 @@
         <v>26</v>
       </c>
       <c r="AJ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AK6" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AL6" t="n">
         <v>29</v>
@@ -1503,7 +1570,7 @@
         <v>19</v>
       </c>
       <c r="AP6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AQ6" t="n">
         <v>6</v>
@@ -1518,22 +1585,22 @@
         <v>6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AV6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AX6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY6" t="n">
         <v>22</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
         <v>18</v>
@@ -1542,7 +1609,7 @@
         <v>29</v>
       </c>
       <c r="BC6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E7" t="n">
         <v>22</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G7" t="n">
-        <v>0.314</v>
+        <v>0.319</v>
       </c>
       <c r="H7" t="n">
         <v>48.1</v>
       </c>
       <c r="I7" t="n">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="J7" t="n">
         <v>84.09999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L7" t="n">
         <v>7</v>
@@ -1601,28 +1668,28 @@
         <v>19.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0.352</v>
+        <v>0.351</v>
       </c>
       <c r="O7" t="n">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="P7" t="n">
-        <v>22.7</v>
+        <v>22.9</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.756</v>
+        <v>0.757</v>
       </c>
       <c r="R7" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S7" t="n">
-        <v>28.3</v>
+        <v>28.2</v>
       </c>
       <c r="T7" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U7" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V7" t="n">
         <v>14.1</v>
@@ -1643,10 +1710,10 @@
         <v>20.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>97.09999999999999</v>
+        <v>97.2</v>
       </c>
       <c r="AC7" t="n">
-        <v>-4.2</v>
+        <v>-4.3</v>
       </c>
       <c r="AD7" t="n">
         <v>26</v>
@@ -1676,19 +1743,19 @@
         <v>16</v>
       </c>
       <c r="AM7" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AN7" t="n">
         <v>22</v>
       </c>
       <c r="AO7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP7" t="n">
         <v>12</v>
       </c>
       <c r="AQ7" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR7" t="n">
         <v>8</v>
@@ -1703,7 +1770,7 @@
         <v>26</v>
       </c>
       <c r="AV7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW7" t="n">
         <v>14</v>
@@ -1715,7 +1782,7 @@
         <v>29</v>
       </c>
       <c r="AZ7" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BA7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1831,16 +1898,16 @@
         <v>-0.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
+        <v>16</v>
+      </c>
+      <c r="AF8" t="n">
         <v>17</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AG8" t="n">
         <v>16</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>17</v>
       </c>
       <c r="AH8" t="n">
         <v>3</v>
@@ -1849,13 +1916,13 @@
         <v>4</v>
       </c>
       <c r="AJ8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK8" t="n">
         <v>8</v>
       </c>
       <c r="AL8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1882,7 +1949,7 @@
         <v>16</v>
       </c>
       <c r="AU8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AV8" t="n">
         <v>8</v>
@@ -1897,7 +1964,7 @@
         <v>4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA8" t="n">
         <v>23</v>
@@ -1906,7 +1973,7 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -1935,46 +2002,46 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" t="n">
         <v>49</v>
       </c>
       <c r="F9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G9" t="n">
-        <v>0.671</v>
+        <v>0.681</v>
       </c>
       <c r="H9" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I9" t="n">
         <v>40.5</v>
       </c>
       <c r="J9" t="n">
-        <v>85.09999999999999</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
         <v>0.476</v>
       </c>
       <c r="L9" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M9" t="n">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="N9" t="n">
-        <v>0.341</v>
+        <v>0.343</v>
       </c>
       <c r="O9" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P9" t="n">
-        <v>26</v>
+        <v>26.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.7</v>
+        <v>0.698</v>
       </c>
       <c r="R9" t="n">
         <v>13.3</v>
@@ -1983,7 +2050,7 @@
         <v>31.5</v>
       </c>
       <c r="T9" t="n">
-        <v>44.8</v>
+        <v>44.9</v>
       </c>
       <c r="U9" t="n">
         <v>24.2</v>
@@ -1992,25 +2059,25 @@
         <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y9" t="n">
         <v>6.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA9" t="n">
         <v>21.8</v>
       </c>
       <c r="AB9" t="n">
-        <v>105.6</v>
+        <v>105.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD9" t="n">
         <v>1</v>
@@ -2019,10 +2086,10 @@
         <v>4</v>
       </c>
       <c r="AF9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AH9" t="n">
         <v>7</v>
@@ -2058,7 +2125,7 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AT9" t="n">
         <v>2</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -2195,31 +2262,31 @@
         <v>-4.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>26</v>
       </c>
       <c r="AF10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG10" t="n">
         <v>26</v>
       </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AJ10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK10" t="n">
         <v>19</v>
       </c>
       <c r="AL10" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AM10" t="n">
         <v>24</v>
@@ -2240,7 +2307,7 @@
         <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT10" t="n">
         <v>14</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" t="n">
         <v>41</v>
       </c>
       <c r="F11" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G11" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
@@ -2317,43 +2384,43 @@
         <v>37.8</v>
       </c>
       <c r="J11" t="n">
-        <v>83.09999999999999</v>
+        <v>83</v>
       </c>
       <c r="K11" t="n">
         <v>0.455</v>
       </c>
       <c r="L11" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.399</v>
+        <v>0.402</v>
       </c>
       <c r="O11" t="n">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="P11" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="Q11" t="n">
         <v>0.791</v>
       </c>
       <c r="R11" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S11" t="n">
-        <v>34</v>
+        <v>34.1</v>
       </c>
       <c r="T11" t="n">
         <v>44.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.5</v>
+        <v>22.3</v>
       </c>
       <c r="V11" t="n">
-        <v>15.2</v>
+        <v>15.3</v>
       </c>
       <c r="W11" t="n">
         <v>6.8</v>
@@ -2362,37 +2429,37 @@
         <v>4.2</v>
       </c>
       <c r="Y11" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z11" t="n">
         <v>21.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>100.5</v>
+        <v>100.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="AD11" t="n">
         <v>1</v>
       </c>
       <c r="AE11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF11" t="n">
         <v>10</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>11</v>
       </c>
       <c r="AG11" t="n">
         <v>10</v>
       </c>
       <c r="AH11" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
@@ -2404,28 +2471,28 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AN11" t="n">
         <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>1</v>
       </c>
       <c r="AT11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
         <v>14</v>
@@ -2434,25 +2501,25 @@
         <v>25</v>
       </c>
       <c r="AW11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX11" t="n">
         <v>27</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>28</v>
       </c>
       <c r="BA11" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="BB11" t="n">
         <v>9</v>
       </c>
       <c r="BC11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -2481,37 +2548,37 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E12" t="n">
         <v>39</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>0.549</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
       </c>
       <c r="I12" t="n">
-        <v>38.1</v>
+        <v>38.2</v>
       </c>
       <c r="J12" t="n">
         <v>82.5</v>
       </c>
       <c r="K12" t="n">
-        <v>0.462</v>
+        <v>0.463</v>
       </c>
       <c r="L12" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="M12" t="n">
-        <v>28.8</v>
+        <v>28.9</v>
       </c>
       <c r="N12" t="n">
-        <v>0.369</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
         <v>19.2</v>
@@ -2520,22 +2587,22 @@
         <v>25.4</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.756</v>
+        <v>0.755</v>
       </c>
       <c r="R12" t="n">
         <v>10.9</v>
       </c>
       <c r="S12" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T12" t="n">
         <v>43.1</v>
       </c>
       <c r="U12" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W12" t="n">
         <v>8.5</v>
@@ -2553,22 +2620,22 @@
         <v>20.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>106.1</v>
+        <v>106.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG12" t="n">
         <v>11</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>13</v>
       </c>
       <c r="AH12" t="n">
         <v>23</v>
@@ -2583,13 +2650,13 @@
         <v>7</v>
       </c>
       <c r="AL12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AM12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
         <v>2</v>
@@ -2601,7 +2668,7 @@
         <v>17</v>
       </c>
       <c r="AR12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
         <v>8</v>
@@ -2631,7 +2698,7 @@
         <v>11</v>
       </c>
       <c r="BB12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BC12" t="n">
         <v>8</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" t="n">
         <v>27</v>
       </c>
       <c r="G13" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
@@ -2681,7 +2748,7 @@
         <v>35.2</v>
       </c>
       <c r="J13" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K13" t="n">
         <v>0.434</v>
@@ -2693,22 +2760,22 @@
         <v>19.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.355</v>
+        <v>0.356</v>
       </c>
       <c r="O13" t="n">
-        <v>17.3</v>
+        <v>17.2</v>
       </c>
       <c r="P13" t="n">
         <v>22.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.752</v>
+        <v>0.75</v>
       </c>
       <c r="R13" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="S13" t="n">
-        <v>33.5</v>
+        <v>33.4</v>
       </c>
       <c r="T13" t="n">
         <v>46.3</v>
@@ -2741,7 +2808,7 @@
         <v>4.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE13" t="n">
         <v>7</v>
@@ -2774,7 +2841,7 @@
         <v>20</v>
       </c>
       <c r="AO13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
         <v>11</v>
@@ -2795,7 +2862,7 @@
         <v>27</v>
       </c>
       <c r="AV13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -2845,67 +2912,67 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14" t="n">
         <v>23</v>
       </c>
       <c r="G14" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H14" t="n">
         <v>48.1</v>
       </c>
       <c r="I14" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J14" t="n">
-        <v>80.40000000000001</v>
+        <v>80.5</v>
       </c>
       <c r="K14" t="n">
         <v>0.476</v>
       </c>
       <c r="L14" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="M14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="N14" t="n">
-        <v>0.355</v>
+        <v>0.354</v>
       </c>
       <c r="O14" t="n">
-        <v>16.7</v>
+        <v>16.5</v>
       </c>
       <c r="P14" t="n">
         <v>23.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.708</v>
+        <v>0.706</v>
       </c>
       <c r="R14" t="n">
         <v>11.4</v>
       </c>
       <c r="S14" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T14" t="n">
         <v>41.5</v>
       </c>
       <c r="U14" t="n">
-        <v>23.5</v>
+        <v>23.6</v>
       </c>
       <c r="V14" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W14" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="Y14" t="n">
         <v>4.2</v>
@@ -2914,25 +2981,25 @@
         <v>20.9</v>
       </c>
       <c r="AA14" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>100.9</v>
+        <v>100.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>4</v>
       </c>
       <c r="AG14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH14" t="n">
         <v>28</v>
@@ -2947,13 +3014,13 @@
         <v>4</v>
       </c>
       <c r="AL14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM14" t="n">
         <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="n">
         <v>17</v>
@@ -2965,10 +3032,10 @@
         <v>27</v>
       </c>
       <c r="AR14" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AS14" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT14" t="n">
         <v>19</v>
@@ -2989,7 +3056,7 @@
         <v>5</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BA14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3027,28 +3094,28 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E15" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F15" t="n">
         <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H15" t="n">
         <v>48.1</v>
       </c>
       <c r="I15" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J15" t="n">
         <v>81.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.458</v>
+        <v>0.457</v>
       </c>
       <c r="L15" t="n">
         <v>8.800000000000001</v>
@@ -3057,16 +3124,16 @@
         <v>24.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O15" t="n">
         <v>18.9</v>
       </c>
       <c r="P15" t="n">
-        <v>27.5</v>
+        <v>27.4</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="R15" t="n">
         <v>11.5</v>
@@ -3078,7 +3145,7 @@
         <v>44.8</v>
       </c>
       <c r="U15" t="n">
-        <v>22.1</v>
+        <v>22</v>
       </c>
       <c r="V15" t="n">
         <v>15.1</v>
@@ -3093,19 +3160,19 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.1</v>
+        <v>18</v>
       </c>
       <c r="AA15" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>102.3</v>
+        <v>102.1</v>
       </c>
       <c r="AC15" t="n">
         <v>0.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE15" t="n">
         <v>14</v>
@@ -3153,25 +3220,25 @@
         <v>3</v>
       </c>
       <c r="AT15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AU15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AV15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AW15" t="n">
         <v>24</v>
       </c>
       <c r="AX15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY15" t="n">
         <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BA15" t="n">
         <v>1</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3209,25 +3276,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
         <v>47</v>
       </c>
       <c r="F16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G16" t="n">
-        <v>0.662</v>
+        <v>0.671</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.2</v>
+        <v>36.3</v>
       </c>
       <c r="J16" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="K16" t="n">
         <v>0.443</v>
@@ -3236,40 +3303,40 @@
         <v>4.7</v>
       </c>
       <c r="M16" t="n">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.346</v>
+        <v>0.347</v>
       </c>
       <c r="O16" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P16" t="n">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.778</v>
+        <v>0.777</v>
       </c>
       <c r="R16" t="n">
         <v>13.2</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U16" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="V16" t="n">
-        <v>14.4</v>
+        <v>14.3</v>
       </c>
       <c r="W16" t="n">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="X16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y16" t="n">
         <v>5.6</v>
@@ -3278,22 +3345,22 @@
         <v>20.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>93.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="AD16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
       </c>
       <c r="AF16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG16" t="n">
         <v>6</v>
@@ -3302,13 +3369,13 @@
         <v>17</v>
       </c>
       <c r="AI16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
         <v>30</v>
@@ -3320,13 +3387,13 @@
         <v>23</v>
       </c>
       <c r="AO16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AR16" t="n">
         <v>2</v>
@@ -3335,19 +3402,19 @@
         <v>26</v>
       </c>
       <c r="AT16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
         <v>24</v>
       </c>
       <c r="AV16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AW16" t="n">
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY16" t="n">
         <v>19</v>
@@ -3356,7 +3423,7 @@
         <v>17</v>
       </c>
       <c r="BA16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3391,25 +3458,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E17" t="n">
         <v>56</v>
       </c>
       <c r="F17" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.789</v>
+        <v>0.8</v>
       </c>
       <c r="H17" t="n">
         <v>48.6</v>
       </c>
       <c r="I17" t="n">
-        <v>38.7</v>
+        <v>38.8</v>
       </c>
       <c r="J17" t="n">
-        <v>78.09999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="K17" t="n">
         <v>0.496</v>
@@ -3421,28 +3488,28 @@
         <v>21.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.391</v>
+        <v>0.392</v>
       </c>
       <c r="O17" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="P17" t="n">
         <v>23.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.759</v>
+        <v>0.76</v>
       </c>
       <c r="R17" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="S17" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T17" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="U17" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V17" t="n">
         <v>13.5</v>
@@ -3451,25 +3518,25 @@
         <v>8.9</v>
       </c>
       <c r="X17" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="Y17" t="n">
         <v>3.3</v>
       </c>
       <c r="Z17" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="AA17" t="n">
         <v>20.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>103.4</v>
+        <v>103.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AD17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>1</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM17" t="n">
         <v>9</v>
@@ -3514,13 +3581,13 @@
         <v>28</v>
       </c>
       <c r="AS17" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT17" t="n">
         <v>30</v>
       </c>
       <c r="AU17" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AV17" t="n">
         <v>3</v>
@@ -3529,7 +3596,7 @@
         <v>3</v>
       </c>
       <c r="AX17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AY17" t="n">
         <v>1</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
         <v>34</v>
       </c>
       <c r="F18" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G18" t="n">
-        <v>0.486</v>
+        <v>0.493</v>
       </c>
       <c r="H18" t="n">
         <v>48.4</v>
@@ -3603,16 +3670,16 @@
         <v>19.2</v>
       </c>
       <c r="N18" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O18" t="n">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="P18" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.739</v>
+        <v>0.737</v>
       </c>
       <c r="R18" t="n">
         <v>12.9</v>
@@ -3624,31 +3691,31 @@
         <v>43.9</v>
       </c>
       <c r="U18" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="V18" t="n">
         <v>14.1</v>
       </c>
       <c r="W18" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="Y18" t="n">
         <v>4.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.59999999999999</v>
+        <v>98.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>-1.6</v>
+        <v>-1.5</v>
       </c>
       <c r="AD18" t="n">
         <v>26</v>
@@ -3657,7 +3724,7 @@
         <v>18</v>
       </c>
       <c r="AF18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AG18" t="n">
         <v>18</v>
@@ -3666,7 +3733,7 @@
         <v>15</v>
       </c>
       <c r="AI18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ18" t="n">
         <v>1</v>
@@ -3681,16 +3748,16 @@
         <v>18</v>
       </c>
       <c r="AN18" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AO18" t="n">
         <v>24</v>
       </c>
       <c r="AP18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR18" t="n">
         <v>3</v>
@@ -3705,10 +3772,10 @@
         <v>11</v>
       </c>
       <c r="AV18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AW18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX18" t="n">
         <v>2</v>
@@ -3720,13 +3787,13 @@
         <v>9</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="BB18" t="n">
         <v>12</v>
       </c>
       <c r="BC18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3755,28 +3822,28 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E19" t="n">
         <v>25</v>
       </c>
       <c r="F19" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G19" t="n">
-        <v>0.357</v>
+        <v>0.362</v>
       </c>
       <c r="H19" t="n">
         <v>48.1</v>
       </c>
       <c r="I19" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J19" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
         <v>5.4</v>
@@ -3785,13 +3852,13 @@
         <v>18</v>
       </c>
       <c r="N19" t="n">
-        <v>0.299</v>
+        <v>0.3</v>
       </c>
       <c r="O19" t="n">
         <v>18.2</v>
       </c>
       <c r="P19" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q19" t="n">
         <v>0.732</v>
@@ -3812,7 +3879,7 @@
         <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="X19" t="n">
         <v>4.9</v>
@@ -3821,13 +3888,13 @@
         <v>5.9</v>
       </c>
       <c r="Z19" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="AA19" t="n">
         <v>22.6</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.3</v>
+        <v>95</v>
       </c>
       <c r="AC19" t="n">
         <v>-2.6</v>
@@ -3836,13 +3903,13 @@
         <v>26</v>
       </c>
       <c r="AE19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF19" t="n">
         <v>21</v>
       </c>
       <c r="AG19" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH19" t="n">
         <v>26</v>
@@ -3866,7 +3933,7 @@
         <v>30</v>
       </c>
       <c r="AO19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AP19" t="n">
         <v>6</v>
@@ -3887,10 +3954,10 @@
         <v>16</v>
       </c>
       <c r="AV19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
@@ -3899,7 +3966,7 @@
         <v>23</v>
       </c>
       <c r="AZ19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BA19" t="n">
         <v>2</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -3937,16 +4004,16 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E20" t="n">
         <v>25</v>
       </c>
       <c r="F20" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G20" t="n">
-        <v>0.347</v>
+        <v>0.352</v>
       </c>
       <c r="H20" t="n">
         <v>48.3</v>
@@ -3955,37 +4022,37 @@
         <v>36.3</v>
       </c>
       <c r="J20" t="n">
-        <v>80.3</v>
+        <v>80.5</v>
       </c>
       <c r="K20" t="n">
         <v>0.451</v>
       </c>
       <c r="L20" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="M20" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N20" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O20" t="n">
         <v>14.9</v>
       </c>
       <c r="P20" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.775</v>
+        <v>0.776</v>
       </c>
       <c r="R20" t="n">
         <v>11.8</v>
       </c>
       <c r="S20" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T20" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U20" t="n">
         <v>21.3</v>
@@ -4000,7 +4067,7 @@
         <v>5.6</v>
       </c>
       <c r="Y20" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z20" t="n">
         <v>20.4</v>
@@ -4012,31 +4079,31 @@
         <v>94.09999999999999</v>
       </c>
       <c r="AC20" t="n">
-        <v>-3.4</v>
+        <v>-3.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE20" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF20" t="n">
         <v>24</v>
       </c>
-      <c r="AF20" t="n">
-        <v>25</v>
-      </c>
       <c r="AG20" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH20" t="n">
         <v>22</v>
       </c>
       <c r="AI20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ20" t="n">
         <v>26</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>19</v>
@@ -4045,13 +4112,13 @@
         <v>21</v>
       </c>
       <c r="AN20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO20" t="n">
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ20" t="n">
         <v>10</v>
@@ -4069,7 +4136,7 @@
         <v>22</v>
       </c>
       <c r="AV20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AW20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -4119,55 +4186,55 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E21" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" t="n">
         <v>26</v>
       </c>
       <c r="G21" t="n">
-        <v>0.629</v>
+        <v>0.623</v>
       </c>
       <c r="H21" t="n">
         <v>48.1</v>
       </c>
       <c r="I21" t="n">
-        <v>36.1</v>
+        <v>36</v>
       </c>
       <c r="J21" t="n">
-        <v>81.40000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K21" t="n">
-        <v>0.443</v>
+        <v>0.442</v>
       </c>
       <c r="L21" t="n">
-        <v>10.7</v>
+        <v>10.6</v>
       </c>
       <c r="M21" t="n">
-        <v>28.9</v>
+        <v>28.8</v>
       </c>
       <c r="N21" t="n">
         <v>0.369</v>
       </c>
       <c r="O21" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="P21" t="n">
         <v>21.6</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.758</v>
+        <v>0.756</v>
       </c>
       <c r="R21" t="n">
         <v>11</v>
       </c>
       <c r="S21" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="T21" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U21" t="n">
         <v>19.3</v>
@@ -4179,22 +4246,22 @@
         <v>8.4</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4</v>
       </c>
       <c r="Z21" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AA21" t="n">
         <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>99.09999999999999</v>
+        <v>99</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD21" t="n">
         <v>26</v>
@@ -4212,34 +4279,34 @@
         <v>30</v>
       </c>
       <c r="AI21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ21" t="n">
         <v>19</v>
       </c>
       <c r="AK21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO21" t="n">
         <v>20</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO21" t="n">
-        <v>21</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
       </c>
       <c r="AQ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>24</v>
@@ -4266,7 +4333,7 @@
         <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BB21" t="n">
         <v>11</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -4301,25 +4368,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E22" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F22" t="n">
         <v>19</v>
       </c>
       <c r="G22" t="n">
-        <v>0.736</v>
+        <v>0.732</v>
       </c>
       <c r="H22" t="n">
         <v>48.4</v>
       </c>
       <c r="I22" t="n">
-        <v>38</v>
+        <v>38.1</v>
       </c>
       <c r="J22" t="n">
-        <v>79</v>
+        <v>79.3</v>
       </c>
       <c r="K22" t="n">
         <v>0.481</v>
@@ -4328,28 +4395,28 @@
         <v>7.3</v>
       </c>
       <c r="M22" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="N22" t="n">
-        <v>0.379</v>
+        <v>0.377</v>
       </c>
       <c r="O22" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="P22" t="n">
-        <v>27.6</v>
+        <v>27.4</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.828</v>
+        <v>0.826</v>
       </c>
       <c r="R22" t="n">
-        <v>10.3</v>
+        <v>10.4</v>
       </c>
       <c r="S22" t="n">
         <v>33.1</v>
       </c>
       <c r="T22" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U22" t="n">
         <v>21.5</v>
@@ -4370,16 +4437,16 @@
         <v>20.2</v>
       </c>
       <c r="AA22" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="AB22" t="n">
         <v>106.2</v>
       </c>
       <c r="AC22" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>3</v>
@@ -4394,7 +4461,7 @@
         <v>12</v>
       </c>
       <c r="AI22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ22" t="n">
         <v>29</v>
@@ -4451,7 +4518,7 @@
         <v>6</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
         <v>18</v>
       </c>
       <c r="F23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G23" t="n">
-        <v>0.25</v>
+        <v>0.254</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.8</v>
+        <v>37.7</v>
       </c>
       <c r="J23" t="n">
         <v>83.8</v>
       </c>
       <c r="K23" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
         <v>6.4</v>
@@ -4528,16 +4595,16 @@
         <v>10.5</v>
       </c>
       <c r="S23" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T23" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="V23" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W23" t="n">
         <v>6.3</v>
@@ -4552,16 +4619,16 @@
         <v>19.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>94.40000000000001</v>
+        <v>94.2</v>
       </c>
       <c r="AC23" t="n">
         <v>-6.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>29</v>
@@ -4576,13 +4643,13 @@
         <v>25</v>
       </c>
       <c r="AI23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AJ23" t="n">
         <v>7</v>
       </c>
       <c r="AK23" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL23" t="n">
         <v>20</v>
@@ -4612,28 +4679,28 @@
         <v>15</v>
       </c>
       <c r="AU23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
       </c>
       <c r="AX23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY23" t="n">
         <v>18</v>
       </c>
       <c r="AZ23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA23" t="n">
         <v>29</v>
       </c>
       <c r="BB23" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC23" t="n">
         <v>29</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -4665,64 +4732,64 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" t="n">
         <v>43</v>
       </c>
       <c r="G24" t="n">
-        <v>0.394</v>
+        <v>0.386</v>
       </c>
       <c r="H24" t="n">
         <v>48.2</v>
       </c>
       <c r="I24" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J24" t="n">
-        <v>84</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="K24" t="n">
         <v>0.444</v>
       </c>
       <c r="L24" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M24" t="n">
         <v>17.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O24" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="P24" t="n">
-        <v>16.6</v>
+        <v>16.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.721</v>
+        <v>0.72</v>
       </c>
       <c r="R24" t="n">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="S24" t="n">
-        <v>30.5</v>
+        <v>30.4</v>
       </c>
       <c r="T24" t="n">
-        <v>41.3</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
-        <v>22.9</v>
+        <v>22.8</v>
       </c>
       <c r="V24" t="n">
         <v>13.2</v>
       </c>
       <c r="W24" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="X24" t="n">
         <v>4.9</v>
@@ -4731,19 +4798,19 @@
         <v>4.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AA24" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="AB24" t="n">
-        <v>92.90000000000001</v>
+        <v>92.8</v>
       </c>
       <c r="AC24" t="n">
-        <v>-3.7</v>
+        <v>-3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE24" t="n">
         <v>20</v>
@@ -4761,19 +4828,19 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK24" t="n">
         <v>18</v>
       </c>
       <c r="AL24" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AM24" t="n">
         <v>25</v>
       </c>
       <c r="AN24" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AO24" t="n">
         <v>30</v>
@@ -4794,7 +4861,7 @@
         <v>21</v>
       </c>
       <c r="AU24" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AV24" t="n">
         <v>2</v>
@@ -4809,7 +4876,7 @@
         <v>13</v>
       </c>
       <c r="AZ24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA24" t="n">
         <v>30</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -4847,25 +4914,25 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E25" t="n">
         <v>23</v>
       </c>
       <c r="F25" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G25" t="n">
-        <v>0.319</v>
+        <v>0.324</v>
       </c>
       <c r="H25" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I25" t="n">
-        <v>37</v>
+        <v>37.1</v>
       </c>
       <c r="J25" t="n">
-        <v>84.2</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K25" t="n">
         <v>0.44</v>
@@ -4889,16 +4956,16 @@
         <v>0.735</v>
       </c>
       <c r="R25" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T25" t="n">
-        <v>41.8</v>
+        <v>41.9</v>
       </c>
       <c r="U25" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="V25" t="n">
         <v>15.4</v>
@@ -4916,22 +4983,22 @@
         <v>20.7</v>
       </c>
       <c r="AA25" t="n">
-        <v>18.3</v>
+        <v>18.4</v>
       </c>
       <c r="AB25" t="n">
-        <v>94.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="AC25" t="n">
-        <v>-6.4</v>
+        <v>-6.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE25" t="n">
         <v>27</v>
       </c>
       <c r="AF25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG25" t="n">
         <v>27</v>
@@ -4970,7 +5037,7 @@
         <v>11</v>
       </c>
       <c r="AS25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT25" t="n">
         <v>17</v>
@@ -4982,7 +5049,7 @@
         <v>28</v>
       </c>
       <c r="AW25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX25" t="n">
         <v>12</v>
@@ -4991,13 +5058,13 @@
         <v>17</v>
       </c>
       <c r="AZ25" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BA25" t="n">
         <v>27</v>
       </c>
       <c r="BB25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC25" t="n">
         <v>28</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
         <v>33</v>
       </c>
       <c r="F26" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G26" t="n">
-        <v>0.465</v>
+        <v>0.471</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
@@ -5056,10 +5123,10 @@
         <v>8.4</v>
       </c>
       <c r="M26" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.357</v>
+        <v>0.356</v>
       </c>
       <c r="O26" t="n">
         <v>16</v>
@@ -5068,13 +5135,13 @@
         <v>20.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.777</v>
+        <v>0.78</v>
       </c>
       <c r="R26" t="n">
         <v>11</v>
       </c>
       <c r="S26" t="n">
-        <v>30.5</v>
+        <v>30.6</v>
       </c>
       <c r="T26" t="n">
         <v>41.6</v>
@@ -5086,7 +5153,7 @@
         <v>14.7</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
         <v>4.7</v>
@@ -5101,13 +5168,13 @@
         <v>18.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="AC26" t="n">
-        <v>-1.6</v>
+        <v>-1.4</v>
       </c>
       <c r="AD26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
         <v>19</v>
@@ -5122,7 +5189,7 @@
         <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ26" t="n">
         <v>11</v>
@@ -5137,7 +5204,7 @@
         <v>4</v>
       </c>
       <c r="AN26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AO26" t="n">
         <v>22</v>
@@ -5146,10 +5213,10 @@
         <v>25</v>
       </c>
       <c r="AQ26" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AR26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS26" t="n">
         <v>15</v>
@@ -5161,13 +5228,13 @@
         <v>19</v>
       </c>
       <c r="AV26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY26" t="n">
         <v>6</v>
@@ -5179,10 +5246,10 @@
         <v>25</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BC26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5211,46 +5278,46 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F27" t="n">
         <v>46</v>
       </c>
       <c r="G27" t="n">
-        <v>0.361</v>
+        <v>0.352</v>
       </c>
       <c r="H27" t="n">
         <v>48.4</v>
       </c>
       <c r="I27" t="n">
-        <v>37.5</v>
+        <v>37.4</v>
       </c>
       <c r="J27" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K27" t="n">
         <v>0.447</v>
       </c>
       <c r="L27" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M27" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="N27" t="n">
         <v>0.367</v>
       </c>
       <c r="O27" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="P27" t="n">
         <v>22.7</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.767</v>
+        <v>0.77</v>
       </c>
       <c r="R27" t="n">
         <v>11.4</v>
@@ -5268,37 +5335,37 @@
         <v>14.8</v>
       </c>
       <c r="W27" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X27" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Y27" t="n">
         <v>6.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AA27" t="n">
         <v>20</v>
       </c>
       <c r="AB27" t="n">
-        <v>99.8</v>
+        <v>99.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>-5</v>
+        <v>-5.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF27" t="n">
         <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>12</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>10</v>
@@ -5331,7 +5398,7 @@
         <v>11</v>
       </c>
       <c r="AR27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AS27" t="n">
         <v>29</v>
@@ -5346,7 +5413,7 @@
         <v>17</v>
       </c>
       <c r="AW27" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX27" t="n">
         <v>25</v>
@@ -5358,7 +5425,7 @@
         <v>25</v>
       </c>
       <c r="BA27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E28" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F28" t="n">
         <v>17</v>
       </c>
       <c r="G28" t="n">
-        <v>0.761</v>
+        <v>0.757</v>
       </c>
       <c r="H28" t="n">
         <v>48.6</v>
@@ -5411,67 +5478,67 @@
         <v>39.5</v>
       </c>
       <c r="J28" t="n">
-        <v>81.2</v>
+        <v>81.3</v>
       </c>
       <c r="K28" t="n">
-        <v>0.486</v>
+        <v>0.487</v>
       </c>
       <c r="L28" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.383</v>
+        <v>0.381</v>
       </c>
       <c r="O28" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P28" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.79</v>
+        <v>0.791</v>
       </c>
       <c r="R28" t="n">
         <v>8</v>
       </c>
       <c r="S28" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T28" t="n">
         <v>41</v>
       </c>
       <c r="U28" t="n">
-        <v>25.1</v>
+        <v>25.2</v>
       </c>
       <c r="V28" t="n">
-        <v>14.8</v>
+        <v>14.7</v>
       </c>
       <c r="W28" t="n">
         <v>8.6</v>
       </c>
       <c r="X28" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z28" t="n">
         <v>17.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="AB28" t="n">
         <v>104.3</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE28" t="n">
         <v>2</v>
@@ -5489,13 +5556,13 @@
         <v>2</v>
       </c>
       <c r="AJ28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AK28" t="n">
         <v>2</v>
       </c>
       <c r="AL28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM28" t="n">
         <v>6</v>
@@ -5504,13 +5571,13 @@
         <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
@@ -5525,13 +5592,13 @@
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW28" t="n">
         <v>4</v>
       </c>
       <c r="AX28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY28" t="n">
         <v>10</v>
@@ -5540,7 +5607,7 @@
         <v>1</v>
       </c>
       <c r="BA28" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB28" t="n">
         <v>4</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5575,46 +5642,46 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" t="n">
         <v>26</v>
       </c>
       <c r="F29" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G29" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="H29" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I29" t="n">
         <v>36.3</v>
       </c>
       <c r="J29" t="n">
-        <v>82</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="K29" t="n">
         <v>0.442</v>
       </c>
       <c r="L29" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="M29" t="n">
         <v>21</v>
       </c>
       <c r="N29" t="n">
-        <v>0.34</v>
+        <v>0.341</v>
       </c>
       <c r="O29" t="n">
         <v>17.5</v>
       </c>
       <c r="P29" t="n">
-        <v>22.2</v>
+        <v>22.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.786</v>
+        <v>0.788</v>
       </c>
       <c r="R29" t="n">
         <v>10.9</v>
@@ -5629,31 +5696,31 @@
         <v>21.5</v>
       </c>
       <c r="V29" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="W29" t="n">
         <v>7.4</v>
       </c>
       <c r="X29" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z29" t="n">
-        <v>22.8</v>
+        <v>22.9</v>
       </c>
       <c r="AA29" t="n">
         <v>20</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.2</v>
+        <v>97.3</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.3</v>
+        <v>-2.1</v>
       </c>
       <c r="AD29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE29" t="n">
         <v>21</v>
@@ -5713,16 +5780,16 @@
         <v>18</v>
       </c>
       <c r="AX29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ29" t="n">
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5757,28 +5824,28 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E30" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F30" t="n">
         <v>36</v>
       </c>
       <c r="G30" t="n">
-        <v>0.5</v>
+        <v>0.493</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J30" t="n">
         <v>82</v>
       </c>
       <c r="K30" t="n">
-        <v>0.451</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
         <v>6</v>
@@ -5790,10 +5857,10 @@
         <v>0.363</v>
       </c>
       <c r="O30" t="n">
-        <v>18.2</v>
+        <v>18.3</v>
       </c>
       <c r="P30" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q30" t="n">
         <v>0.766</v>
@@ -5802,13 +5869,13 @@
         <v>12.4</v>
       </c>
       <c r="S30" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T30" t="n">
         <v>42.5</v>
       </c>
       <c r="U30" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V30" t="n">
         <v>15.1</v>
@@ -5817,31 +5884,31 @@
         <v>8.300000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z30" t="n">
-        <v>21.6</v>
+        <v>21.7</v>
       </c>
       <c r="AA30" t="n">
         <v>20.6</v>
       </c>
       <c r="AB30" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC30" t="n">
-        <v>-0.5</v>
+        <v>-0.7</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>16</v>
       </c>
       <c r="AF30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG30" t="n">
         <v>16</v>
@@ -5850,10 +5917,10 @@
         <v>6</v>
       </c>
       <c r="AI30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AJ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AK30" t="n">
         <v>14</v>
@@ -5868,7 +5935,7 @@
         <v>12</v>
       </c>
       <c r="AO30" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AP30" t="n">
         <v>7</v>
@@ -5880,7 +5947,7 @@
         <v>7</v>
       </c>
       <c r="AS30" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="n">
         <v>13</v>
@@ -5907,10 +5974,10 @@
         <v>9</v>
       </c>
       <c r="BB30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BC30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
@@ -5939,28 +6006,28 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
         <v>26</v>
       </c>
       <c r="F31" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G31" t="n">
-        <v>0.366</v>
+        <v>0.371</v>
       </c>
       <c r="H31" t="n">
         <v>48.5</v>
       </c>
       <c r="I31" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J31" t="n">
         <v>81.59999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.434</v>
+        <v>0.436</v>
       </c>
       <c r="L31" t="n">
         <v>6.7</v>
@@ -5969,22 +6036,22 @@
         <v>18.4</v>
       </c>
       <c r="N31" t="n">
-        <v>0.365</v>
+        <v>0.367</v>
       </c>
       <c r="O31" t="n">
-        <v>15.3</v>
+        <v>15.2</v>
       </c>
       <c r="P31" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="Q31" t="n">
         <v>0.735</v>
       </c>
       <c r="R31" t="n">
-        <v>10.8</v>
+        <v>10.7</v>
       </c>
       <c r="S31" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T31" t="n">
         <v>43.2</v>
@@ -5993,7 +6060,7 @@
         <v>22</v>
       </c>
       <c r="V31" t="n">
-        <v>15.4</v>
+        <v>15.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.3</v>
@@ -6002,22 +6069,22 @@
         <v>4.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="AA31" t="n">
         <v>18.9</v>
       </c>
       <c r="AB31" t="n">
-        <v>92.90000000000001</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>-2.5</v>
+        <v>-2.2</v>
       </c>
       <c r="AD31" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>21</v>
@@ -6032,13 +6099,13 @@
         <v>8</v>
       </c>
       <c r="AI31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AJ31" t="n">
         <v>17</v>
       </c>
       <c r="AK31" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AL31" t="n">
         <v>18</v>
@@ -6059,7 +6126,7 @@
         <v>23</v>
       </c>
       <c r="AR31" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AS31" t="n">
         <v>7</v>
@@ -6068,7 +6135,7 @@
         <v>8</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>27</v>
@@ -6083,13 +6150,13 @@
         <v>9</v>
       </c>
       <c r="AZ31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA31" t="n">
         <v>24</v>
       </c>
       <c r="BB31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC31" t="n">
         <v>21</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-27-2012-13</t>
+          <t>2013-03-27</t>
         </is>
       </c>
     </row>
